--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/138.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/138.xlsx
@@ -426,13 +426,13 @@
         <v>-16.17517872520538</v>
       </c>
       <c r="E2">
-        <v>-18.84469871427287</v>
+        <v>-13.4432753006179</v>
       </c>
       <c r="F2">
-        <v>2.745521720140909</v>
+        <v>4.04549525270223</v>
       </c>
       <c r="G2">
-        <v>-10.99914635143866</v>
+        <v>-7.576585193300697</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.93932813859646</v>
       </c>
       <c r="E3">
-        <v>-19.58418946277742</v>
+        <v>-14.19717565341486</v>
       </c>
       <c r="F3">
-        <v>2.755389232643057</v>
+        <v>4.034791089123254</v>
       </c>
       <c r="G3">
-        <v>-10.09504629630032</v>
+        <v>-7.651357174850676</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.64605332953263</v>
       </c>
       <c r="E4">
-        <v>-20.12033814291555</v>
+        <v>-15.0275755176234</v>
       </c>
       <c r="F4">
-        <v>2.92399844727848</v>
+        <v>4.16752371154343</v>
       </c>
       <c r="G4">
-        <v>-10.06759194214314</v>
+        <v>-7.470541798586763</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.32333890188239</v>
       </c>
       <c r="E5">
-        <v>-21.25264231226746</v>
+        <v>-16.75940888932479</v>
       </c>
       <c r="F5">
-        <v>3.042877453254237</v>
+        <v>4.178993286602593</v>
       </c>
       <c r="G5">
-        <v>-9.915452511340398</v>
+        <v>-6.586169284316936</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.96712393428473</v>
       </c>
       <c r="E6">
-        <v>-21.5650436201606</v>
+        <v>-18.19512534566461</v>
       </c>
       <c r="F6">
-        <v>2.797130666070124</v>
+        <v>4.349095219297859</v>
       </c>
       <c r="G6">
-        <v>-9.09554956090234</v>
+        <v>-6.325602866011979</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.58575507933043</v>
       </c>
       <c r="E7">
-        <v>-22.10173118870565</v>
+        <v>-18.2350846003083</v>
       </c>
       <c r="F7">
-        <v>2.951472080559728</v>
+        <v>4.210522606687947</v>
       </c>
       <c r="G7">
-        <v>-9.358929942915676</v>
+        <v>-5.441465400475441</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.17260896790202</v>
       </c>
       <c r="E8">
-        <v>-22.61950332132065</v>
+        <v>-18.59808707676315</v>
       </c>
       <c r="F8">
-        <v>3.273935629651908</v>
+        <v>4.661124652584377</v>
       </c>
       <c r="G8">
-        <v>-9.355450559553901</v>
+        <v>-5.616136404218468</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.71880386813119</v>
       </c>
       <c r="E9">
-        <v>-23.53259312090925</v>
+        <v>-18.50269930026559</v>
       </c>
       <c r="F9">
-        <v>3.227386351818993</v>
+        <v>4.375092701867319</v>
       </c>
       <c r="G9">
-        <v>-8.635509531674137</v>
+        <v>-4.549372694008035</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.22148153132194</v>
       </c>
       <c r="E10">
-        <v>-24.3898015512432</v>
+        <v>-20.24543270890344</v>
       </c>
       <c r="F10">
-        <v>3.098843611722177</v>
+        <v>4.670256574832839</v>
       </c>
       <c r="G10">
-        <v>-7.572658886291122</v>
+        <v>-3.695000343415084</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.67028795008672</v>
       </c>
       <c r="E11">
-        <v>-25.80660710012699</v>
+        <v>-21.25955729207717</v>
       </c>
       <c r="F11">
-        <v>3.165381394984644</v>
+        <v>4.142382760868466</v>
       </c>
       <c r="G11">
-        <v>-7.397848839635446</v>
+        <v>-3.879238823766604</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.07037467942596</v>
       </c>
       <c r="E12">
-        <v>-26.04852723856476</v>
+        <v>-21.19345515698721</v>
       </c>
       <c r="F12">
-        <v>3.4057852124207</v>
+        <v>4.720965913762614</v>
       </c>
       <c r="G12">
-        <v>-7.112052753775703</v>
+        <v>-3.547585061096877</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.40703971682778</v>
       </c>
       <c r="E13">
-        <v>-26.61795114571125</v>
+        <v>-22.90646819071272</v>
       </c>
       <c r="F13">
-        <v>3.568324150728408</v>
+        <v>4.886533363294956</v>
       </c>
       <c r="G13">
-        <v>-6.495937055098561</v>
+        <v>-2.412471827682651</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.68049093187235</v>
       </c>
       <c r="E14">
-        <v>-26.89605831994431</v>
+        <v>-23.48634834434292</v>
       </c>
       <c r="F14">
-        <v>4.087775124941116</v>
+        <v>4.981828749313012</v>
       </c>
       <c r="G14">
-        <v>-6.555473906076814</v>
+        <v>-1.362376714262448</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.879628120466961</v>
       </c>
       <c r="E15">
-        <v>-28.66297377978312</v>
+        <v>-24.60273945603187</v>
       </c>
       <c r="F15">
-        <v>4.030283113717219</v>
+        <v>5.216702385967977</v>
       </c>
       <c r="G15">
-        <v>-5.585189424517361</v>
+        <v>-1.072055112650522</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.002294335504473</v>
       </c>
       <c r="E16">
-        <v>-29.62426465670936</v>
+        <v>-26.65642053240641</v>
       </c>
       <c r="F16">
-        <v>4.015097482489098</v>
+        <v>5.678112969736135</v>
       </c>
       <c r="G16">
-        <v>-5.089001548545856</v>
+        <v>-0.4495699243558218</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.062153592730002</v>
       </c>
       <c r="E17">
-        <v>-30.28875255446188</v>
+        <v>-27.13114046263049</v>
       </c>
       <c r="F17">
-        <v>4.464970565071066</v>
+        <v>6.20449572237547</v>
       </c>
       <c r="G17">
-        <v>-4.472485273858461</v>
+        <v>-0.0929314745012154</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.07703539233445</v>
       </c>
       <c r="E18">
-        <v>-30.39176854542536</v>
+        <v>-28.09111808209451</v>
       </c>
       <c r="F18">
-        <v>4.372779900078703</v>
+        <v>6.167154576592075</v>
       </c>
       <c r="G18">
-        <v>-4.313910142527372</v>
+        <v>0.02491401506022104</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.091694274798142</v>
       </c>
       <c r="E19">
-        <v>-31.09768745187406</v>
+        <v>-28.83985144604872</v>
       </c>
       <c r="F19">
-        <v>4.899580149889048</v>
+        <v>6.46093838946453</v>
       </c>
       <c r="G19">
-        <v>-4.333068269563134</v>
+        <v>0.954535065760806</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.142961526175643</v>
       </c>
       <c r="E20">
-        <v>-32.08871908184567</v>
+        <v>-29.22750240652733</v>
       </c>
       <c r="F20">
-        <v>5.044251203318371</v>
+        <v>6.601939775299451</v>
       </c>
       <c r="G20">
-        <v>-3.821731337203924</v>
+        <v>1.060512249563955</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.282100972399071</v>
       </c>
       <c r="E21">
-        <v>-32.47954450260365</v>
+        <v>-30.57689482709593</v>
       </c>
       <c r="F21">
-        <v>5.19779241489687</v>
+        <v>7.126640942111102</v>
       </c>
       <c r="G21">
-        <v>-3.400682913337258</v>
+        <v>1.466610249775273</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.544181293798076</v>
       </c>
       <c r="E22">
-        <v>-33.28254257059178</v>
+        <v>-30.0932334249437</v>
       </c>
       <c r="F22">
-        <v>4.895294176946964</v>
+        <v>7.154919748507872</v>
       </c>
       <c r="G22">
-        <v>-2.863189360672266</v>
+        <v>1.793606074871245</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.951474594961613</v>
       </c>
       <c r="E23">
-        <v>-33.03894689677117</v>
+        <v>-28.9125153399758</v>
       </c>
       <c r="F23">
-        <v>5.63752296699896</v>
+        <v>6.872189670258373</v>
       </c>
       <c r="G23">
-        <v>-2.260027826690291</v>
+        <v>1.5037380179982</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.514291418865841</v>
       </c>
       <c r="E24">
-        <v>-33.67240569062313</v>
+        <v>-30.32591094793181</v>
       </c>
       <c r="F24">
-        <v>5.393658230554008</v>
+        <v>6.800250931529653</v>
       </c>
       <c r="G24">
-        <v>-3.461954490178089</v>
+        <v>2.621351707691838</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.219372603809267</v>
       </c>
       <c r="E25">
-        <v>-33.62655715553247</v>
+        <v>-30.85365930878572</v>
       </c>
       <c r="F25">
-        <v>5.766572667946289</v>
+        <v>6.685712570744565</v>
       </c>
       <c r="G25">
-        <v>-2.436526251570996</v>
+        <v>2.146559887540643</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.050924837781996</v>
       </c>
       <c r="E26">
-        <v>-34.01335449866063</v>
+        <v>-30.04893589220067</v>
       </c>
       <c r="F26">
-        <v>5.338566828063424</v>
+        <v>6.232163193628974</v>
       </c>
       <c r="G26">
-        <v>-2.497887213141387</v>
+        <v>1.671777999026066</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.976203570405501</v>
       </c>
       <c r="E27">
-        <v>-33.23683215395835</v>
+        <v>-30.15092391956442</v>
       </c>
       <c r="F27">
-        <v>5.2594958459966</v>
+        <v>6.719158732999998</v>
       </c>
       <c r="G27">
-        <v>-2.536054492663645</v>
+        <v>1.735466274110565</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.967255078689074</v>
       </c>
       <c r="E28">
-        <v>-33.28946887158651</v>
+        <v>-31.04968336315574</v>
       </c>
       <c r="F28">
-        <v>4.886602946156791</v>
+        <v>6.796770131703089</v>
       </c>
       <c r="G28">
-        <v>-3.067496368082848</v>
+        <v>2.53444657674043</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.9952044884014</v>
       </c>
       <c r="E29">
-        <v>-33.20556304093539</v>
+        <v>-30.54995719946131</v>
       </c>
       <c r="F29">
-        <v>5.086743137612374</v>
+        <v>6.707722292636948</v>
       </c>
       <c r="G29">
-        <v>-3.427177209288045</v>
+        <v>1.874250964207892</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.037314539278405</v>
       </c>
       <c r="E30">
-        <v>-32.82488140195458</v>
+        <v>-29.35474346919484</v>
       </c>
       <c r="F30">
-        <v>4.530318812743113</v>
+        <v>6.593134229807692</v>
       </c>
       <c r="G30">
-        <v>-3.204999877056477</v>
+        <v>1.628525721555488</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.081652131167985</v>
       </c>
       <c r="E31">
-        <v>-32.41960562063813</v>
+        <v>-30.02786490264298</v>
       </c>
       <c r="F31">
-        <v>5.039473180139024</v>
+        <v>6.775459551898669</v>
       </c>
       <c r="G31">
-        <v>-3.467734702689656</v>
+        <v>0.8776641983389291</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.12052272870827</v>
       </c>
       <c r="E32">
-        <v>-33.27903300323583</v>
+        <v>-29.05111834392856</v>
       </c>
       <c r="F32">
-        <v>4.954580431965325</v>
+        <v>6.297995207864257</v>
       </c>
       <c r="G32">
-        <v>-3.365097859335632</v>
+        <v>0.7794005856422817</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.154245779230496</v>
       </c>
       <c r="E33">
-        <v>-31.69820159732021</v>
+        <v>-29.35237960576284</v>
       </c>
       <c r="F33">
-        <v>4.970914180413725</v>
+        <v>6.417147575082937</v>
       </c>
       <c r="G33">
-        <v>-4.202543390586289</v>
+        <v>0.1657181379365032</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.185649257129774</v>
       </c>
       <c r="E34">
-        <v>-32.15856852917698</v>
+        <v>-29.27389662273591</v>
       </c>
       <c r="F34">
-        <v>5.292816096406807</v>
+        <v>6.221442462701943</v>
       </c>
       <c r="G34">
-        <v>-3.78986071529736</v>
+        <v>1.452788722148816</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.218778123841474</v>
       </c>
       <c r="E35">
-        <v>-31.71642870520108</v>
+        <v>-28.01581408782096</v>
       </c>
       <c r="F35">
-        <v>5.404241452492174</v>
+        <v>6.519293559522144</v>
       </c>
       <c r="G35">
-        <v>-4.84969214314856</v>
+        <v>-0.1000226630463343</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.260531681068904</v>
       </c>
       <c r="E36">
-        <v>-31.26702294467988</v>
+        <v>-28.11260569126091</v>
       </c>
       <c r="F36">
-        <v>4.953503554341685</v>
+        <v>6.857613717438713</v>
       </c>
       <c r="G36">
-        <v>-5.397087537521512</v>
+        <v>0.6624224590121343</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.315060989310951</v>
       </c>
       <c r="E37">
-        <v>-31.14640251101157</v>
+        <v>-27.91186749544889</v>
       </c>
       <c r="F37">
-        <v>5.193640637474039</v>
+        <v>6.645760410907545</v>
       </c>
       <c r="G37">
-        <v>-4.724533658490873</v>
+        <v>0.4941043921589693</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.386195708930556</v>
       </c>
       <c r="E38">
-        <v>-29.80708594511002</v>
+        <v>-26.71658130959831</v>
       </c>
       <c r="F38">
-        <v>5.205434932555098</v>
+        <v>7.140043926688398</v>
       </c>
       <c r="G38">
-        <v>-4.739454287236368</v>
+        <v>-0.1577254717958311</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.475923687637238</v>
       </c>
       <c r="E39">
-        <v>-29.36895382063091</v>
+        <v>-25.63212499661145</v>
       </c>
       <c r="F39">
-        <v>5.641398069709256</v>
+        <v>6.905571219856387</v>
       </c>
       <c r="G39">
-        <v>-4.896721753079446</v>
+        <v>-0.6000375296612366</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.584207697427682</v>
       </c>
       <c r="E40">
-        <v>-29.4808252425164</v>
+        <v>-26.50105311767725</v>
       </c>
       <c r="F40">
-        <v>5.553158717228247</v>
+        <v>7.202098585566915</v>
       </c>
       <c r="G40">
-        <v>-5.506587141778445</v>
+        <v>-0.9493828476928285</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.713981934715157</v>
       </c>
       <c r="E41">
-        <v>-28.72572484410741</v>
+        <v>-26.16297536216061</v>
       </c>
       <c r="F41">
-        <v>5.796720271203775</v>
+        <v>6.892647031637909</v>
       </c>
       <c r="G41">
-        <v>-5.472068083440464</v>
+        <v>-0.7701730860154614</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.86483461205887</v>
       </c>
       <c r="E42">
-        <v>-28.52140462535533</v>
+        <v>-25.33692283299943</v>
       </c>
       <c r="F42">
-        <v>5.483189836183384</v>
+        <v>6.783893988793974</v>
       </c>
       <c r="G42">
-        <v>-4.968729429104134</v>
+        <v>-0.882662112894357</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.03968027375383</v>
       </c>
       <c r="E43">
-        <v>-27.52183908611626</v>
+        <v>-25.44548394038532</v>
       </c>
       <c r="F43">
-        <v>5.868667293606523</v>
+        <v>7.090966471542139</v>
       </c>
       <c r="G43">
-        <v>-5.59200914832826</v>
+        <v>-0.5172805122705354</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.235762994006769</v>
       </c>
       <c r="E44">
-        <v>-27.67753707944798</v>
+        <v>-24.72148057298699</v>
       </c>
       <c r="F44">
-        <v>5.850290791142819</v>
+        <v>7.086788186362418</v>
       </c>
       <c r="G44">
-        <v>-6.148607859300385</v>
+        <v>-1.571997147263561</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.44899882066799</v>
       </c>
       <c r="E45">
-        <v>-26.38017908946451</v>
+        <v>-23.8132905822747</v>
       </c>
       <c r="F45">
-        <v>5.710121086180309</v>
+        <v>7.144777218027995</v>
       </c>
       <c r="G45">
-        <v>-5.586113066722818</v>
+        <v>-1.37549971678012</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.672964682018334</v>
       </c>
       <c r="E46">
-        <v>-25.9817820601657</v>
+        <v>-22.40898815012608</v>
       </c>
       <c r="F46">
-        <v>5.92958874587801</v>
+        <v>7.39619997865609</v>
       </c>
       <c r="G46">
-        <v>-5.675613665377014</v>
+        <v>-0.8208145011296928</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.897636514820337</v>
       </c>
       <c r="E47">
-        <v>-25.94140165743931</v>
+        <v>-22.62994145390833</v>
       </c>
       <c r="F47">
-        <v>5.823294297485583</v>
+        <v>7.209404786059607</v>
       </c>
       <c r="G47">
-        <v>-5.427438619025549</v>
+        <v>-1.32844031193938</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.118037176190312</v>
       </c>
       <c r="E48">
-        <v>-24.97872506746672</v>
+        <v>-21.68647465067628</v>
       </c>
       <c r="F48">
-        <v>5.893705526723541</v>
+        <v>7.528914376993404</v>
       </c>
       <c r="G48">
-        <v>-6.436605457943743</v>
+        <v>-1.968090678855201</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.325118620304171</v>
       </c>
       <c r="E49">
-        <v>-24.84591398176976</v>
+        <v>-20.80455886615649</v>
       </c>
       <c r="F49">
-        <v>6.270359214572059</v>
+        <v>7.133960396482239</v>
       </c>
       <c r="G49">
-        <v>-5.769927797245311</v>
+        <v>-2.315661544477744</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.517266998739923</v>
       </c>
       <c r="E50">
-        <v>-24.36646179620766</v>
+        <v>-20.95914285488233</v>
       </c>
       <c r="F50">
-        <v>6.217984857162658</v>
+        <v>7.162621908619101</v>
       </c>
       <c r="G50">
-        <v>-5.538967587698057</v>
+        <v>-1.810515332276971</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.692778646200757</v>
       </c>
       <c r="E51">
-        <v>-23.96594091259926</v>
+        <v>-21.18834250983254</v>
       </c>
       <c r="F51">
-        <v>6.069594434094765</v>
+        <v>7.354052645201651</v>
       </c>
       <c r="G51">
-        <v>-6.625965352244515</v>
+        <v>-2.008737556986373</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.85567018746628</v>
       </c>
       <c r="E52">
-        <v>-23.54395053372049</v>
+        <v>-19.3605960586487</v>
       </c>
       <c r="F52">
-        <v>5.876329692082418</v>
+        <v>7.643060091629565</v>
       </c>
       <c r="G52">
-        <v>-6.08753491519191</v>
+        <v>-2.462467686416725</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.013444919209078</v>
       </c>
       <c r="E53">
-        <v>-23.57990208886738</v>
+        <v>-19.62570651247974</v>
       </c>
       <c r="F53">
-        <v>6.016318812951118</v>
+        <v>7.767189290204265</v>
       </c>
       <c r="G53">
-        <v>-6.393104889557719</v>
+        <v>-3.722461318663338</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.171403983574106</v>
       </c>
       <c r="E54">
-        <v>-22.85508359614768</v>
+        <v>-18.62436581142967</v>
       </c>
       <c r="F54">
-        <v>5.829583262807637</v>
+        <v>7.204591971449342</v>
       </c>
       <c r="G54">
-        <v>-7.09966800291329</v>
+        <v>-2.924871445159967</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.340694222092915</v>
       </c>
       <c r="E55">
-        <v>-23.1601442476744</v>
+        <v>-18.80446322271472</v>
       </c>
       <c r="F55">
-        <v>5.858702033750845</v>
+        <v>7.175010971495372</v>
       </c>
       <c r="G55">
-        <v>-7.582186636353144</v>
+        <v>-3.238065605902718</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.523646745907169</v>
       </c>
       <c r="E56">
-        <v>-22.71226458289377</v>
+        <v>-18.17639104869488</v>
       </c>
       <c r="F56">
-        <v>5.748794246747407</v>
+        <v>7.458973660440236</v>
       </c>
       <c r="G56">
-        <v>-7.85270455454915</v>
+        <v>-3.184378488892357</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.725852828095622</v>
       </c>
       <c r="E57">
-        <v>-21.75416628014294</v>
+        <v>-17.35126232823128</v>
       </c>
       <c r="F57">
-        <v>5.990689125508501</v>
+        <v>7.481917780762977</v>
       </c>
       <c r="G57">
-        <v>-7.940685612800821</v>
+        <v>-4.202454005856729</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.945337872599048</v>
       </c>
       <c r="E58">
-        <v>-22.37955306907622</v>
+        <v>-16.94667487496398</v>
       </c>
       <c r="F58">
-        <v>6.346413282557887</v>
+        <v>7.287490010917099</v>
       </c>
       <c r="G58">
-        <v>-7.878195755201538</v>
+        <v>-3.821300966283819</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.179587356358619</v>
       </c>
       <c r="E59">
-        <v>-21.28467220892371</v>
+        <v>-16.09537610321005</v>
       </c>
       <c r="F59">
-        <v>5.954863892072228</v>
+        <v>7.350954551115181</v>
       </c>
       <c r="G59">
-        <v>-8.211349195000555</v>
+        <v>-3.753550651822634</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.424237414380272</v>
       </c>
       <c r="E60">
-        <v>-21.06368267734939</v>
+        <v>-16.84275545343596</v>
       </c>
       <c r="F60">
-        <v>5.946343304967033</v>
+        <v>7.151544979708867</v>
       </c>
       <c r="G60">
-        <v>-8.315376467481073</v>
+        <v>-4.001146352704726</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.670379976934168</v>
       </c>
       <c r="E61">
-        <v>-20.79814654696163</v>
+        <v>-15.77845990673125</v>
       </c>
       <c r="F61">
-        <v>5.847883555470283</v>
+        <v>7.388936853268343</v>
       </c>
       <c r="G61">
-        <v>-8.400606462389609</v>
+        <v>-5.28807789400439</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.914392618629408</v>
       </c>
       <c r="E62">
-        <v>-20.34864116001225</v>
+        <v>-16.90489517376922</v>
       </c>
       <c r="F62">
-        <v>5.666116553008793</v>
+        <v>7.202839146025018</v>
       </c>
       <c r="G62">
-        <v>-8.865360708465735</v>
+        <v>-4.760668263052018</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.145906666834573</v>
       </c>
       <c r="E63">
-        <v>-20.70414901198442</v>
+        <v>-14.92091184084673</v>
       </c>
       <c r="F63">
-        <v>6.003629881075035</v>
+        <v>7.246644871019861</v>
       </c>
       <c r="G63">
-        <v>-9.095559492538957</v>
+        <v>-5.193356565034763</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.36222176915943</v>
       </c>
       <c r="E64">
-        <v>-20.09010605044034</v>
+        <v>-14.40605604549267</v>
       </c>
       <c r="F64">
-        <v>5.731537697012287</v>
+        <v>6.891783872804193</v>
       </c>
       <c r="G64">
-        <v>-9.152447907085794</v>
+        <v>-5.799226125267861</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.557936732431259</v>
       </c>
       <c r="E65">
-        <v>-20.4562331739605</v>
+        <v>-14.62695500758683</v>
       </c>
       <c r="F65">
-        <v>5.702408985660245</v>
+        <v>6.967294531773784</v>
       </c>
       <c r="G65">
-        <v>-9.297784166805338</v>
+        <v>-5.079546630485698</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.731749551943881</v>
       </c>
       <c r="E66">
-        <v>-19.25711137062541</v>
+        <v>-15.51961233245281</v>
       </c>
       <c r="F66">
-        <v>5.667952215173397</v>
+        <v>7.103284294821767</v>
       </c>
       <c r="G66">
-        <v>-9.502779767688088</v>
+        <v>-5.894811506623238</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.882804962249849</v>
       </c>
       <c r="E67">
-        <v>-18.89950230671369</v>
+        <v>-14.09586463291526</v>
       </c>
       <c r="F67">
-        <v>5.634845683553112</v>
+        <v>6.718225991304445</v>
       </c>
       <c r="G67">
-        <v>-9.315661112717402</v>
+        <v>-5.594227213839571</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.008424835071139</v>
       </c>
       <c r="E68">
-        <v>-19.85985578952035</v>
+        <v>-13.53870836185555</v>
       </c>
       <c r="F68">
-        <v>5.709839441263357</v>
+        <v>6.955339533416582</v>
       </c>
       <c r="G68">
-        <v>-9.540400807196365</v>
+        <v>-6.13572983715262</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.111145655328766</v>
       </c>
       <c r="E69">
-        <v>-18.60375219774675</v>
+        <v>-12.92285401070841</v>
       </c>
       <c r="F69">
-        <v>5.408802443411989</v>
+        <v>6.763945244999756</v>
       </c>
       <c r="G69">
-        <v>-9.147018612401387</v>
+        <v>-5.793690893126199</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.187399310587972</v>
       </c>
       <c r="E70">
-        <v>-17.83723098789041</v>
+        <v>-14.09796131638081</v>
       </c>
       <c r="F70">
-        <v>5.705936174061366</v>
+        <v>6.216010029274384</v>
       </c>
       <c r="G70">
-        <v>-9.416983669492335</v>
+        <v>-5.25414149168132</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.239809290012424</v>
       </c>
       <c r="E71">
-        <v>-19.13301306891922</v>
+        <v>-14.19132939347096</v>
       </c>
       <c r="F71">
-        <v>5.407747103340822</v>
+        <v>6.085383116792124</v>
       </c>
       <c r="G71">
-        <v>-9.130177867243116</v>
+        <v>-5.412988087746631</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.26584277093537</v>
       </c>
       <c r="E72">
-        <v>-18.25521366727239</v>
+        <v>-13.4779905823607</v>
       </c>
       <c r="F72">
-        <v>5.00498824516048</v>
+        <v>6.206833375186171</v>
       </c>
       <c r="G72">
-        <v>-9.241034795171151</v>
+        <v>-6.146052118144068</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.26588385402057</v>
       </c>
       <c r="E73">
-        <v>-18.32326304618566</v>
+        <v>-13.25020381130088</v>
       </c>
       <c r="F73">
-        <v>5.27567551810808</v>
+        <v>6.278072971826928</v>
       </c>
       <c r="G73">
-        <v>-9.820628555459054</v>
+        <v>-5.156831316099983</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.236601024413389</v>
       </c>
       <c r="E74">
-        <v>-18.57424918958678</v>
+        <v>-13.7699367731612</v>
       </c>
       <c r="F74">
-        <v>5.077332883916572</v>
+        <v>6.039607534113423</v>
       </c>
       <c r="G74">
-        <v>-9.146581620390204</v>
+        <v>-5.282681704775378</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.174498677186419</v>
       </c>
       <c r="E75">
-        <v>-19.43490378864056</v>
+        <v>-14.87507009846708</v>
       </c>
       <c r="F75">
-        <v>4.887065175167553</v>
+        <v>6.399990429436154</v>
       </c>
       <c r="G75">
-        <v>-8.988231606155784</v>
+        <v>-5.268754239691663</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.077956825704451</v>
       </c>
       <c r="E76">
-        <v>-18.87897020556291</v>
+        <v>-14.09872662848811</v>
       </c>
       <c r="F76">
-        <v>4.994028944421443</v>
+        <v>6.009408572076964</v>
       </c>
       <c r="G76">
-        <v>-9.664814419107715</v>
+        <v>-4.757692082612214</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.941933292150837</v>
       </c>
       <c r="E77">
-        <v>-19.55273468232014</v>
+        <v>-14.40792630525783</v>
       </c>
       <c r="F77">
-        <v>4.837086456287048</v>
+        <v>5.793837552642032</v>
       </c>
       <c r="G77">
-        <v>-9.326132368258117</v>
+        <v>-4.891391774761219</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.767467948126255</v>
       </c>
       <c r="E78">
-        <v>-19.53086215286309</v>
+        <v>-13.89309315227381</v>
       </c>
       <c r="F78">
-        <v>4.892959837605875</v>
+        <v>5.706249296939624</v>
       </c>
       <c r="G78">
-        <v>-9.010948569646263</v>
+        <v>-4.906196534412841</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.550096686997998</v>
       </c>
       <c r="E79">
-        <v>-20.0198830040034</v>
+        <v>-14.9868373654504</v>
       </c>
       <c r="F79">
-        <v>4.688026712357694</v>
+        <v>5.859387921960363</v>
       </c>
       <c r="G79">
-        <v>-8.468889774682617</v>
+        <v>-3.893964130325282</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.293074865676517</v>
       </c>
       <c r="E80">
-        <v>-19.40681819284499</v>
+        <v>-15.49520385755147</v>
       </c>
       <c r="F80">
-        <v>4.455427772590816</v>
+        <v>5.760563690806382</v>
       </c>
       <c r="G80">
-        <v>-8.469303592875026</v>
+        <v>-3.88189057074356</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.995768253996681</v>
       </c>
       <c r="E81">
-        <v>-20.56901481912152</v>
+        <v>-15.78826405295786</v>
       </c>
       <c r="F81">
-        <v>4.667980221209945</v>
+        <v>5.462112855986554</v>
       </c>
       <c r="G81">
-        <v>-8.007081914136444</v>
+        <v>-3.19689897212188</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.66344111232686</v>
       </c>
       <c r="E82">
-        <v>-21.25288684986387</v>
+        <v>-15.26555135520048</v>
       </c>
       <c r="F82">
-        <v>4.42588653427218</v>
+        <v>5.398885228865673</v>
       </c>
       <c r="G82">
-        <v>-8.318398995558427</v>
+        <v>-3.270429499094633</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.301587631752366</v>
       </c>
       <c r="E83">
-        <v>-22.15900732795466</v>
+        <v>-15.81365973519287</v>
       </c>
       <c r="F83">
-        <v>4.444438650625277</v>
+        <v>4.947027377986599</v>
       </c>
       <c r="G83">
-        <v>-8.343042696552763</v>
+        <v>-3.195180798986998</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.914088866427502</v>
       </c>
       <c r="E84">
-        <v>-22.85059587840608</v>
+        <v>-17.36569457489372</v>
       </c>
       <c r="F84">
-        <v>4.421940191965242</v>
+        <v>5.3884776208169</v>
       </c>
       <c r="G84">
-        <v>-7.638734064709436</v>
+        <v>-3.16710406226844</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.509276731527877</v>
       </c>
       <c r="E85">
-        <v>-22.81572210007301</v>
+        <v>-18.65570738003675</v>
       </c>
       <c r="F85">
-        <v>4.114872679421493</v>
+        <v>5.296354881951567</v>
       </c>
       <c r="G85">
-        <v>-7.353788789053286</v>
+        <v>-2.707103759586708</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.087933170532209</v>
       </c>
       <c r="E86">
-        <v>-23.97651037093316</v>
+        <v>-19.20824007913464</v>
       </c>
       <c r="F86">
-        <v>4.11494557575294</v>
+        <v>5.213523111876033</v>
       </c>
       <c r="G86">
-        <v>-7.009144445687459</v>
+        <v>-1.76904743885206</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.659346808910456</v>
       </c>
       <c r="E87">
-        <v>-25.83891776217172</v>
+        <v>-20.2765252114401</v>
       </c>
       <c r="F87">
-        <v>4.012595812932644</v>
+        <v>4.850053719610472</v>
       </c>
       <c r="G87">
-        <v>-6.742873957418338</v>
+        <v>-2.080738611919982</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.226148928935502</v>
       </c>
       <c r="E88">
-        <v>-26.51103387439015</v>
+        <v>-21.92439161809127</v>
       </c>
       <c r="F88">
-        <v>3.889058068683543</v>
+        <v>4.660952352164595</v>
       </c>
       <c r="G88">
-        <v>-6.404076037474864</v>
+        <v>-1.699201549064517</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.797540602968275</v>
       </c>
       <c r="E89">
-        <v>-27.50378858872169</v>
+        <v>-22.50643638229714</v>
       </c>
       <c r="F89">
-        <v>3.697488166377323</v>
+        <v>4.405454023914727</v>
       </c>
       <c r="G89">
-        <v>-6.827978151596382</v>
+        <v>-2.42342311232656</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.38200872582875</v>
       </c>
       <c r="E90">
-        <v>-29.36981423069237</v>
+        <v>-25.16254488438607</v>
       </c>
       <c r="F90">
-        <v>3.278924058151567</v>
+        <v>4.521599417461245</v>
       </c>
       <c r="G90">
-        <v>-6.532925780408838</v>
+        <v>-1.293540540864383</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.987049785632555</v>
       </c>
       <c r="E91">
-        <v>-30.05612484468785</v>
+        <v>-27.18594858354533</v>
       </c>
       <c r="F91">
-        <v>3.346649720269649</v>
+        <v>4.234127764198122</v>
       </c>
       <c r="G91">
-        <v>-6.329764221754844</v>
+        <v>-1.568994482459442</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.624655600742969</v>
       </c>
       <c r="E92">
-        <v>-31.95282410534949</v>
+        <v>-27.56548904707619</v>
       </c>
       <c r="F92">
-        <v>3.40600721488465</v>
+        <v>4.075475525744349</v>
       </c>
       <c r="G92">
-        <v>-5.534855890138282</v>
+        <v>-1.565544894007521</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.299480761646575</v>
       </c>
       <c r="E93">
-        <v>-33.30998965155226</v>
+        <v>-29.59108679189217</v>
       </c>
       <c r="F93">
-        <v>2.701528784113033</v>
+        <v>3.782899472545175</v>
       </c>
       <c r="G93">
-        <v>-5.973254883176269</v>
+        <v>-1.258879129068213</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.021202420457758</v>
       </c>
       <c r="E94">
-        <v>-35.64912308700031</v>
+        <v>-31.59110771551281</v>
       </c>
       <c r="F94">
-        <v>2.614699312951589</v>
+        <v>3.190113132162626</v>
       </c>
       <c r="G94">
-        <v>-5.916366468629433</v>
+        <v>-1.137243064864311</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.790878701055828</v>
       </c>
       <c r="E95">
-        <v>-37.97143776998386</v>
+        <v>-33.78924937696904</v>
       </c>
       <c r="F95">
-        <v>2.108084720012662</v>
+        <v>3.078187442165969</v>
       </c>
       <c r="G95">
-        <v>-5.876014229051256</v>
+        <v>-1.139083728184146</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.614739711287704</v>
       </c>
       <c r="E96">
-        <v>-39.19764437635881</v>
+        <v>-35.34798182972723</v>
       </c>
       <c r="F96">
-        <v>2.090483569437978</v>
+        <v>2.536097186834749</v>
       </c>
       <c r="G96">
-        <v>-5.571397691800757</v>
+        <v>-1.751352572944656</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.489898064774465</v>
       </c>
       <c r="E97">
-        <v>-41.8201357516518</v>
+        <v>-38.09824409914664</v>
       </c>
       <c r="F97">
-        <v>1.18346599521227</v>
+        <v>1.940327067067317</v>
       </c>
       <c r="G97">
-        <v>-6.291653221506754</v>
+        <v>-2.235274877693161</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.423711324030605</v>
       </c>
       <c r="E98">
-        <v>-43.90509273376032</v>
+        <v>-41.26926953098874</v>
       </c>
       <c r="F98">
-        <v>0.7641099677494374</v>
+        <v>1.963175096771333</v>
       </c>
       <c r="G98">
-        <v>-6.740626096997173</v>
+        <v>-1.852870451906407</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.405096752386461</v>
       </c>
       <c r="E99">
-        <v>-47.43000935235384</v>
+        <v>-42.74116849464986</v>
       </c>
       <c r="F99">
-        <v>0.5404714781786408</v>
+        <v>1.468961163852314</v>
       </c>
       <c r="G99">
-        <v>-6.258792746483948</v>
+        <v>-1.572672498553572</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.452364366810748</v>
       </c>
       <c r="E100">
-        <v>-48.6207308364047</v>
+        <v>-46.01064295141871</v>
       </c>
       <c r="F100">
-        <v>0.4714924961801232</v>
+        <v>1.337939948486322</v>
       </c>
       <c r="G100">
-        <v>-6.092874825146755</v>
+        <v>-1.602454166224856</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.535754366229049</v>
       </c>
       <c r="E101">
-        <v>-50.40508318541004</v>
+        <v>-48.41640608917861</v>
       </c>
       <c r="F101">
-        <v>-0.3483717152296454</v>
+        <v>0.6709285753433266</v>
       </c>
       <c r="G101">
-        <v>-6.301323325026964</v>
+        <v>-1.444938409466333</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.711005368548711</v>
       </c>
       <c r="E102">
-        <v>-53.28058153563008</v>
+        <v>-50.25243059084848</v>
       </c>
       <c r="F102">
-        <v>-0.6464489563508111</v>
+        <v>0.3982167724632846</v>
       </c>
       <c r="G102">
-        <v>-5.83961147030143</v>
+        <v>-1.634675705958582</v>
       </c>
     </row>
   </sheetData>
